--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -28961,6 +28961,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1245" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29007,6 +29007,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29030,6 +29030,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1247" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>0.236000001430511</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>0.236000001430511</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29053,6 +29053,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29055,13 +29055,13 @@
     </row>
     <row r="1248">
       <c r="A1248" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="B1248" t="n">
-        <v>1500</v>
+        <v>25500</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.237000003457069</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1248" t="n">
         <v>0.237000003457069</v>
@@ -29070,7 +29070,7 @@
         <v>0.237000003457069</v>
       </c>
       <c r="F1248" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1248" t="s">
         <v>7</v>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29076,6 +29076,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>0.238999992609024</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29099,6 +29099,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>105000</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29122,6 +29122,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>0.243000000715256</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1252" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>0.248999997973442</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>0.250999987125397</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>0.248999997973442</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29168,6 +29168,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1253" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29191,6 +29191,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1254">
+      <c r="A1254" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1254" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29214,6 +29214,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1255">
+      <c r="A1255" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1255" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1256" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1256" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29260,6 +29260,27 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1257" t="n">
+        <v>126000</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F1257"/>
+      <c r="G1257" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29276,8 +29276,33 @@
       <c r="E1257" t="n">
         <v>0.24600000679493</v>
       </c>
-      <c r="F1257"/>
+      <c r="F1257" t="n">
+        <v>0.254000008106232</v>
+      </c>
       <c r="G1257" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1258" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>0.250999987125397</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>0.250999987125397</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="G1258" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29306,6 +29306,27 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1259">
+      <c r="A1259" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1259" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="F1259"/>
+      <c r="G1259" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29322,8 +29322,31 @@
       <c r="E1259" t="n">
         <v>0.256000012159348</v>
       </c>
-      <c r="F1259"/>
+      <c r="F1259" t="n">
+        <v>0.256000012159348</v>
+      </c>
       <c r="G1259" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1260" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="F1260"/>
+      <c r="G1260" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29337,7 +29337,7 @@
         <v>21000</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.261000007390976</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1260" t="n">
         <v>0.261000007390976</v>
@@ -29345,8 +29345,31 @@
       <c r="E1260" t="n">
         <v>0.261000007390976</v>
       </c>
-      <c r="F1260"/>
+      <c r="F1260" t="n">
+        <v>0.263999998569489</v>
+      </c>
       <c r="G1260" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1261" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="F1261"/>
+      <c r="G1261" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29368,8 +29368,31 @@
       <c r="E1261" t="n">
         <v>0.266000002622604</v>
       </c>
-      <c r="F1261"/>
+      <c r="F1261" t="n">
+        <v>0.264999985694885</v>
+      </c>
       <c r="G1261" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1262" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F1262"/>
+      <c r="G1262" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -28894,7 +28894,7 @@
     </row>
     <row r="1241">
       <c r="A1241" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1241" t="n">
         <v>0</v>
@@ -28917,22 +28917,22 @@
     </row>
     <row r="1242">
       <c r="A1242" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1242" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.245000004768372</v>
+        <v>0.254999995231628</v>
       </c>
       <c r="D1242" t="n">
-        <v>0.244000002741814</v>
+        <v>0.254999995231628</v>
       </c>
       <c r="E1242" t="n">
-        <v>0.245000004768372</v>
+        <v>0.254999995231628</v>
       </c>
       <c r="F1242" t="n">
-        <v>0.244000002741814</v>
+        <v>0.254999995231628</v>
       </c>
       <c r="G1242" t="s">
         <v>7</v>
@@ -28940,19 +28940,19 @@
     </row>
     <row r="1243">
       <c r="A1243" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1243" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.244000002741814</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="D1243" t="n">
         <v>0.244000002741814</v>
       </c>
       <c r="E1243" t="n">
-        <v>0.244000002741814</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="F1243" t="n">
         <v>0.244000002741814</v>
@@ -28963,10 +28963,10 @@
     </row>
     <row r="1244">
       <c r="A1244" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1244" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C1244" t="n">
         <v>0.244000002741814</v>
@@ -28986,22 +28986,22 @@
     </row>
     <row r="1245">
       <c r="A1245" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1245" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.25</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1245" t="n">
-        <v>0.25</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="E1245" t="n">
-        <v>0.25</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="F1245" t="n">
-        <v>0.25</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="G1245" t="s">
         <v>7</v>
@@ -29009,22 +29009,22 @@
     </row>
     <row r="1246">
       <c r="A1246" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1246" t="n">
-        <v>19500</v>
+        <v>6000</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.24600000679493</v>
+        <v>0.25</v>
       </c>
       <c r="D1246" t="n">
-        <v>0.243000000715256</v>
+        <v>0.25</v>
       </c>
       <c r="E1246" t="n">
-        <v>0.24600000679493</v>
+        <v>0.25</v>
       </c>
       <c r="F1246" t="n">
-        <v>0.243000000715256</v>
+        <v>0.25</v>
       </c>
       <c r="G1246" t="s">
         <v>7</v>
@@ -29032,22 +29032,22 @@
     </row>
     <row r="1247">
       <c r="A1247" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1247" t="n">
-        <v>9000</v>
+        <v>19500</v>
       </c>
       <c r="C1247" t="n">
         <v>0.24600000679493</v>
       </c>
       <c r="D1247" t="n">
-        <v>0.236000001430511</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1247" t="n">
         <v>0.24600000679493</v>
       </c>
       <c r="F1247" t="n">
-        <v>0.236000001430511</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1247" t="s">
         <v>7</v>
@@ -29055,22 +29055,22 @@
     </row>
     <row r="1248">
       <c r="A1248" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1248" t="n">
-        <v>25500</v>
+        <v>9000</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.244000002741814</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="D1248" t="n">
-        <v>0.237000003457069</v>
+        <v>0.236000001430511</v>
       </c>
       <c r="E1248" t="n">
-        <v>0.237000003457069</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1248" t="n">
-        <v>0.238999992609024</v>
+        <v>0.236000001430511</v>
       </c>
       <c r="G1248" t="s">
         <v>7</v>
@@ -29078,22 +29078,22 @@
     </row>
     <row r="1249">
       <c r="A1249" s="1" t="n">
-        <v>46286.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B1249" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.245000004768372</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.238999992609024</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="E1249" t="n">
-        <v>0.245000004768372</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="F1249" t="n">
-        <v>0.239999994635582</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="G1249" t="s">
         <v>7</v>
@@ -29101,22 +29101,22 @@
     </row>
     <row r="1250">
       <c r="A1250" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="B1250" t="n">
-        <v>105000</v>
+        <v>25500</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.263999998569489</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.239999994635582</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="E1250" t="n">
-        <v>0.239999994635582</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="F1250" t="n">
-        <v>0.243000000715256</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1250" t="s">
         <v>7</v>
@@ -29124,22 +29124,22 @@
     </row>
     <row r="1251">
       <c r="A1251" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46286.2916666667</v>
       </c>
       <c r="B1251" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.243000000715256</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.243000000715256</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="E1251" t="n">
-        <v>0.243000000715256</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="F1251" t="n">
-        <v>0.243000000715256</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="G1251" t="s">
         <v>7</v>
@@ -29147,22 +29147,22 @@
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
-        <v>46289.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="B1252" t="n">
-        <v>27000</v>
+        <v>105000</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.252000004053116</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.248999997973442</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1252" t="n">
-        <v>0.250999987125397</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1252" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1252" t="s">
         <v>7</v>
@@ -29170,22 +29170,22 @@
     </row>
     <row r="1253">
       <c r="A1253" s="1" t="n">
-        <v>46290.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="B1253" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.247999995946884</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1253" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="F1253" t="n">
-        <v>0.241999998688698</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1253" t="s">
         <v>7</v>
@@ -29193,22 +29193,22 @@
     </row>
     <row r="1254">
       <c r="A1254" s="1" t="n">
-        <v>46293.2916666667</v>
+        <v>46289.2916666667</v>
       </c>
       <c r="B1254" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.252000004053116</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="E1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="G1254" t="s">
         <v>7</v>
@@ -29216,19 +29216,19 @@
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
-        <v>46294.2916666667</v>
+        <v>46290.2916666667</v>
       </c>
       <c r="B1255" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1255" t="n">
         <v>0.241999998688698</v>
@@ -29239,10 +29239,10 @@
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
-        <v>46295.2916666667</v>
+        <v>46293.2916666667</v>
       </c>
       <c r="B1256" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C1256" t="n">
         <v>0.241999998688698</v>
@@ -29262,22 +29262,22 @@
     </row>
     <row r="1257">
       <c r="A1257" s="1" t="n">
-        <v>46296.2916666667</v>
+        <v>46294.2916666667</v>
       </c>
       <c r="B1257" t="n">
-        <v>126000</v>
+        <v>0</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.261000007390976</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1257" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1257" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1257" t="n">
-        <v>0.254000008106232</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1257" t="s">
         <v>7</v>
@@ -29285,22 +29285,22 @@
     </row>
     <row r="1258">
       <c r="A1258" s="1" t="n">
-        <v>46297.2916666667</v>
+        <v>46295.2916666667</v>
       </c>
       <c r="B1258" t="n">
-        <v>42000</v>
+        <v>6000</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.259999990463257</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.250999987125397</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1258" t="n">
-        <v>0.250999987125397</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1258" t="n">
-        <v>0.257999986410141</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1258" t="s">
         <v>7</v>
@@ -29308,22 +29308,22 @@
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
-        <v>46300.2916666667</v>
+        <v>46296.2916666667</v>
       </c>
       <c r="B1259" t="n">
-        <v>13500</v>
+        <v>126000</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.256000012159348</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.256000012159348</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="E1259" t="n">
-        <v>0.256000012159348</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1259" t="n">
-        <v>0.256000012159348</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="G1259" t="s">
         <v>7</v>
@@ -29331,22 +29331,22 @@
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
-        <v>46301.2916666667</v>
+        <v>46297.2916666667</v>
       </c>
       <c r="B1260" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.261000007390976</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="E1260" t="n">
-        <v>0.261000007390976</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1260" t="n">
-        <v>0.263999998569489</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="G1260" t="s">
         <v>7</v>
@@ -29354,22 +29354,22 @@
     </row>
     <row r="1261">
       <c r="A1261" s="1" t="n">
-        <v>46302.2916666667</v>
+        <v>46300.2916666667</v>
       </c>
       <c r="B1261" t="n">
         <v>13500</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.266000002622604</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.264999985694885</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1261" t="n">
-        <v>0.266000002622604</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1261" t="n">
-        <v>0.264999985694885</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1261" t="s">
         <v>7</v>
@@ -29377,22 +29377,91 @@
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
-        <v>46303.2916666667</v>
+        <v>46301.2916666667</v>
       </c>
       <c r="B1262" t="n">
-        <v>10500</v>
+        <v>21000</v>
       </c>
       <c r="C1262" t="n">
         <v>0.263999998569489</v>
       </c>
       <c r="D1262" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1263" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1264" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="D1264" t="n">
         <v>0.259999990463257</v>
       </c>
-      <c r="E1262" t="n">
+      <c r="E1264" t="n">
         <v>0.259999990463257</v>
       </c>
-      <c r="F1262"/>
-      <c r="G1262" t="s">
+      <c r="F1264" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1265" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F1265"/>
+      <c r="G1265" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29444,6 +29444,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1265" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29467,6 +29467,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1266" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1266" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1267" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C1267" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29078,13 +29078,13 @@
     </row>
     <row r="1249">
       <c r="A1249" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B1249" t="n">
-        <v>25500</v>
+        <v>1500</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.244000002741814</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="D1249" t="n">
         <v>0.237000003457069</v>
@@ -29093,7 +29093,7 @@
         <v>0.237000003457069</v>
       </c>
       <c r="F1249" t="n">
-        <v>0.238999992609024</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="G1249" t="s">
         <v>7</v>
@@ -29101,22 +29101,22 @@
     </row>
     <row r="1250">
       <c r="A1250" s="1" t="n">
-        <v>46286.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="B1250" t="n">
-        <v>15000</v>
+        <v>25500</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.245000004768372</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1250" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="F1250" t="n">
         <v>0.238999992609024</v>
-      </c>
-      <c r="E1250" t="n">
-        <v>0.245000004768372</v>
-      </c>
-      <c r="F1250" t="n">
-        <v>0.239999994635582</v>
       </c>
       <c r="G1250" t="s">
         <v>7</v>
@@ -29124,22 +29124,22 @@
     </row>
     <row r="1251">
       <c r="A1251" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46286.2916666667</v>
       </c>
       <c r="B1251" t="n">
-        <v>105000</v>
+        <v>15000</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.263999998569489</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="D1251" t="n">
+        <v>0.238999992609024</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="F1251" t="n">
         <v>0.239999994635582</v>
-      </c>
-      <c r="E1251" t="n">
-        <v>0.239999994635582</v>
-      </c>
-      <c r="F1251" t="n">
-        <v>0.243000000715256</v>
       </c>
       <c r="G1251" t="s">
         <v>7</v>
@@ -29147,19 +29147,19 @@
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="B1252" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1252" t="n">
         <v>0.243000000715256</v>
@@ -29170,22 +29170,22 @@
     </row>
     <row r="1253">
       <c r="A1253" s="1" t="n">
-        <v>46289.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="B1253" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.252000004053116</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1253" t="n">
-        <v>0.250999987125397</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="F1253" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1253" t="s">
         <v>7</v>
@@ -29193,22 +29193,22 @@
     </row>
     <row r="1254">
       <c r="A1254" s="1" t="n">
-        <v>46290.2916666667</v>
+        <v>46289.2916666667</v>
       </c>
       <c r="B1254" t="n">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.247999995946884</v>
+        <v>0.252000004053116</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.239999994635582</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="E1254" t="n">
-        <v>0.239999994635582</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="G1254" t="s">
         <v>7</v>
@@ -29216,19 +29216,19 @@
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
-        <v>46293.2916666667</v>
+        <v>46290.2916666667</v>
       </c>
       <c r="B1255" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1255" t="n">
         <v>0.241999998688698</v>
@@ -29239,7 +29239,7 @@
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
-        <v>46294.2916666667</v>
+        <v>46293.2916666667</v>
       </c>
       <c r="B1256" t="n">
         <v>0</v>
@@ -29262,10 +29262,10 @@
     </row>
     <row r="1257">
       <c r="A1257" s="1" t="n">
-        <v>46295.2916666667</v>
+        <v>46294.2916666667</v>
       </c>
       <c r="B1257" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C1257" t="n">
         <v>0.241999998688698</v>
@@ -29285,22 +29285,22 @@
     </row>
     <row r="1258">
       <c r="A1258" s="1" t="n">
-        <v>46296.2916666667</v>
+        <v>46295.2916666667</v>
       </c>
       <c r="B1258" t="n">
-        <v>126000</v>
+        <v>6000</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.261000007390976</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1258" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1258" t="n">
-        <v>0.254000008106232</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1258" t="s">
         <v>7</v>
@@ -29308,22 +29308,22 @@
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
-        <v>46297.2916666667</v>
+        <v>46296.2916666667</v>
       </c>
       <c r="B1259" t="n">
-        <v>42000</v>
+        <v>126000</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.250999987125397</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="E1259" t="n">
-        <v>0.250999987125397</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1259" t="n">
-        <v>0.257999986410141</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="G1259" t="s">
         <v>7</v>
@@ -29331,22 +29331,22 @@
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
-        <v>46300.2916666667</v>
+        <v>46297.2916666667</v>
       </c>
       <c r="B1260" t="n">
-        <v>13500</v>
+        <v>42000</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="E1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="G1260" t="s">
         <v>7</v>
@@ -29354,22 +29354,22 @@
     </row>
     <row r="1261">
       <c r="A1261" s="1" t="n">
-        <v>46301.2916666667</v>
+        <v>46300.2916666667</v>
       </c>
       <c r="B1261" t="n">
-        <v>21000</v>
+        <v>13500</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.263999998569489</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.261000007390976</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1261" t="n">
-        <v>0.261000007390976</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1261" t="n">
-        <v>0.263999998569489</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1261" t="s">
         <v>7</v>
@@ -29377,22 +29377,22 @@
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
-        <v>46302.2916666667</v>
+        <v>46301.2916666667</v>
       </c>
       <c r="B1262" t="n">
-        <v>13500</v>
+        <v>21000</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.266000002622604</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.264999985694885</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="E1262" t="n">
-        <v>0.266000002622604</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="F1262" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1262" t="s">
         <v>7</v>
@@ -29400,22 +29400,22 @@
     </row>
     <row r="1263">
       <c r="A1263" s="1" t="n">
-        <v>46303.2916666667</v>
+        <v>46302.2916666667</v>
       </c>
       <c r="B1263" t="n">
-        <v>10500</v>
+        <v>13500</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.263999998569489</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="D1263" t="n">
-        <v>0.259999990463257</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="E1263" t="n">
-        <v>0.259999990463257</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="F1263" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="G1263" t="s">
         <v>7</v>
@@ -29423,13 +29423,13 @@
     </row>
     <row r="1264">
       <c r="A1264" s="1" t="n">
-        <v>46304.2916666667</v>
+        <v>46303.2916666667</v>
       </c>
       <c r="B1264" t="n">
-        <v>1500</v>
+        <v>10500</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.259999990463257</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1264" t="n">
         <v>0.259999990463257</v>
@@ -29438,7 +29438,7 @@
         <v>0.259999990463257</v>
       </c>
       <c r="F1264" t="n">
-        <v>0.259999990463257</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1264" t="s">
         <v>7</v>
@@ -29446,13 +29446,13 @@
     </row>
     <row r="1265">
       <c r="A1265" s="1" t="n">
-        <v>46307.2916666667</v>
+        <v>46304.2916666667</v>
       </c>
       <c r="B1265" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.261999994516373</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1265" t="n">
         <v>0.259999990463257</v>
@@ -29461,7 +29461,7 @@
         <v>0.259999990463257</v>
       </c>
       <c r="F1265" t="n">
-        <v>0.261999994516373</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="G1265" t="s">
         <v>7</v>
@@ -29469,22 +29469,22 @@
     </row>
     <row r="1266">
       <c r="A1266" s="1" t="n">
-        <v>46308.2916666667</v>
+        <v>46307.2916666667</v>
       </c>
       <c r="B1266" t="n">
-        <v>10500</v>
+        <v>18000</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="D1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="G1266" t="s">
         <v>7</v>
@@ -29492,24 +29492,47 @@
     </row>
     <row r="1267">
       <c r="A1267" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1267" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1267" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="n">
         <v>46309.2916666667</v>
       </c>
-      <c r="B1267" t="n">
+      <c r="B1268" t="n">
         <v>16500</v>
       </c>
-      <c r="C1267" t="n">
+      <c r="C1268" t="n">
         <v>0.259999990463257</v>
       </c>
-      <c r="D1267" t="n">
+      <c r="D1268" t="n">
         <v>0.256000012159348</v>
       </c>
-      <c r="E1267" t="n">
+      <c r="E1268" t="n">
         <v>0.259999990463257</v>
       </c>
-      <c r="F1267" t="n">
+      <c r="F1268" t="n">
         <v>0.256000012159348</v>
       </c>
-      <c r="G1267" t="s">
+      <c r="G1268" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -29078,13 +29078,13 @@
     </row>
     <row r="1249">
       <c r="A1249" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="B1249" t="n">
-        <v>1500</v>
+        <v>25500</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.237000003457069</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1249" t="n">
         <v>0.237000003457069</v>
@@ -29093,7 +29093,7 @@
         <v>0.237000003457069</v>
       </c>
       <c r="F1249" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1249" t="s">
         <v>7</v>
@@ -29101,22 +29101,22 @@
     </row>
     <row r="1250">
       <c r="A1250" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46286.2916666667</v>
       </c>
       <c r="B1250" t="n">
-        <v>25500</v>
+        <v>15000</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.244000002741814</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="E1250" t="n">
-        <v>0.237000003457069</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="F1250" t="n">
-        <v>0.238999992609024</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="G1250" t="s">
         <v>7</v>
@@ -29124,22 +29124,22 @@
     </row>
     <row r="1251">
       <c r="A1251" s="1" t="n">
-        <v>46286.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="B1251" t="n">
-        <v>15000</v>
+        <v>105000</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.245000004768372</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.238999992609024</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1251" t="n">
-        <v>0.245000004768372</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1251" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1251" t="s">
         <v>7</v>
@@ -29147,19 +29147,19 @@
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="B1252" t="n">
-        <v>105000</v>
+        <v>0</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.263999998569489</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1252" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="F1252" t="n">
         <v>0.243000000715256</v>
@@ -29170,22 +29170,22 @@
     </row>
     <row r="1253">
       <c r="A1253" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46289.2916666667</v>
       </c>
       <c r="B1253" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.252000004053116</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="E1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="G1253" t="s">
         <v>7</v>
@@ -29193,22 +29193,22 @@
     </row>
     <row r="1254">
       <c r="A1254" s="1" t="n">
-        <v>46289.2916666667</v>
+        <v>46290.2916666667</v>
       </c>
       <c r="B1254" t="n">
-        <v>27000</v>
+        <v>9000</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.252000004053116</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.248999997973442</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="E1254" t="n">
-        <v>0.250999987125397</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1254" t="n">
-        <v>0.248999997973442</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1254" t="s">
         <v>7</v>
@@ -29216,19 +29216,19 @@
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
-        <v>46290.2916666667</v>
+        <v>46293.2916666667</v>
       </c>
       <c r="B1255" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.247999995946884</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.239999994635582</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1255" t="n">
-        <v>0.239999994635582</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1255" t="n">
         <v>0.241999998688698</v>
@@ -29239,7 +29239,7 @@
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
-        <v>46293.2916666667</v>
+        <v>46294.2916666667</v>
       </c>
       <c r="B1256" t="n">
         <v>0</v>
@@ -29262,10 +29262,10 @@
     </row>
     <row r="1257">
       <c r="A1257" s="1" t="n">
-        <v>46294.2916666667</v>
+        <v>46295.2916666667</v>
       </c>
       <c r="B1257" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C1257" t="n">
         <v>0.241999998688698</v>
@@ -29285,22 +29285,22 @@
     </row>
     <row r="1258">
       <c r="A1258" s="1" t="n">
-        <v>46295.2916666667</v>
+        <v>46296.2916666667</v>
       </c>
       <c r="B1258" t="n">
-        <v>6000</v>
+        <v>126000</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="E1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="G1258" t="s">
         <v>7</v>
@@ -29308,22 +29308,22 @@
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
-        <v>46296.2916666667</v>
+        <v>46297.2916666667</v>
       </c>
       <c r="B1259" t="n">
-        <v>126000</v>
+        <v>42000</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.261000007390976</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.24600000679493</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="E1259" t="n">
-        <v>0.24600000679493</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1259" t="n">
-        <v>0.254000008106232</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="G1259" t="s">
         <v>7</v>
@@ -29331,22 +29331,22 @@
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
-        <v>46297.2916666667</v>
+        <v>46300.2916666667</v>
       </c>
       <c r="B1260" t="n">
-        <v>42000</v>
+        <v>13500</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.250999987125397</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1260" t="n">
-        <v>0.250999987125397</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1260" t="n">
-        <v>0.257999986410141</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1260" t="s">
         <v>7</v>
@@ -29354,22 +29354,22 @@
     </row>
     <row r="1261">
       <c r="A1261" s="1" t="n">
-        <v>46300.2916666667</v>
+        <v>46301.2916666667</v>
       </c>
       <c r="B1261" t="n">
-        <v>13500</v>
+        <v>21000</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="E1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="F1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1261" t="s">
         <v>7</v>
@@ -29377,22 +29377,22 @@
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
-        <v>46301.2916666667</v>
+        <v>46302.2916666667</v>
       </c>
       <c r="B1262" t="n">
-        <v>21000</v>
+        <v>13500</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.263999998569489</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.261000007390976</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="E1262" t="n">
-        <v>0.261000007390976</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="F1262" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="G1262" t="s">
         <v>7</v>
@@ -29400,22 +29400,22 @@
     </row>
     <row r="1263">
       <c r="A1263" s="1" t="n">
-        <v>46302.2916666667</v>
+        <v>46303.2916666667</v>
       </c>
       <c r="B1263" t="n">
-        <v>13500</v>
+        <v>10500</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.266000002622604</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="D1263" t="n">
-        <v>0.264999985694885</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1263" t="n">
-        <v>0.266000002622604</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F1263" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1263" t="s">
         <v>7</v>
@@ -29423,13 +29423,13 @@
     </row>
     <row r="1264">
       <c r="A1264" s="1" t="n">
-        <v>46303.2916666667</v>
+        <v>46304.2916666667</v>
       </c>
       <c r="B1264" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1264" t="n">
         <v>0.259999990463257</v>
@@ -29438,7 +29438,7 @@
         <v>0.259999990463257</v>
       </c>
       <c r="F1264" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="G1264" t="s">
         <v>7</v>
@@ -29446,13 +29446,13 @@
     </row>
     <row r="1265">
       <c r="A1265" s="1" t="n">
-        <v>46304.2916666667</v>
+        <v>46307.2916666667</v>
       </c>
       <c r="B1265" t="n">
-        <v>1500</v>
+        <v>18000</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="D1265" t="n">
         <v>0.259999990463257</v>
@@ -29461,7 +29461,7 @@
         <v>0.259999990463257</v>
       </c>
       <c r="F1265" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="G1265" t="s">
         <v>7</v>
@@ -29469,22 +29469,22 @@
     </row>
     <row r="1266">
       <c r="A1266" s="1" t="n">
-        <v>46307.2916666667</v>
+        <v>46308.2916666667</v>
       </c>
       <c r="B1266" t="n">
-        <v>18000</v>
+        <v>10500</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.261999994516373</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="D1266" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="E1266" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="F1266" t="n">
-        <v>0.261999994516373</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="G1266" t="s">
         <v>7</v>
@@ -29492,22 +29492,22 @@
     </row>
     <row r="1267">
       <c r="A1267" s="1" t="n">
-        <v>46308.2916666667</v>
+        <v>46309.2916666667</v>
       </c>
       <c r="B1267" t="n">
-        <v>10500</v>
+        <v>16500</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1267" t="s">
         <v>7</v>
@@ -29515,24 +29515,47 @@
     </row>
     <row r="1268">
       <c r="A1268" s="1" t="n">
-        <v>46309.2916666667</v>
+        <v>46310.2916666667</v>
       </c>
       <c r="B1268" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1268" t="n">
         <v>0.256000012159348</v>
       </c>
       <c r="E1268" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1268" t="n">
         <v>0.256000012159348</v>
       </c>
       <c r="G1268" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1269" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C1269" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>0.24099999666214</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>0.252999991178513</v>
+      </c>
+      <c r="G1269" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -36575,25 +36575,25 @@
         <v>9</v>
       </c>
       <c r="B1249" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="C1249" t="n">
         <v>0.237000003457069</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.237000003457069</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="E1249" t="n">
         <v>0.237000003457069</v>
       </c>
       <c r="F1249" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="H1249" t="n">
-        <v>1500</v>
+        <v>25500</v>
       </c>
       <c r="I1249" t="s">
         <v>9</v>
@@ -36604,25 +36604,25 @@
         <v>9</v>
       </c>
       <c r="B1250" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46286.2916666667</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.237000003457069</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.244000002741814</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="E1250" t="n">
-        <v>0.237000003457069</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="F1250" t="n">
-        <v>0.238999992609024</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.238999992609024</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="H1250" t="n">
-        <v>25500</v>
+        <v>15000</v>
       </c>
       <c r="I1250" t="s">
         <v>9</v>
@@ -36633,25 +36633,25 @@
         <v>9</v>
       </c>
       <c r="B1251" s="1" t="n">
-        <v>46286.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.245000004768372</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.245000004768372</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1251" t="n">
-        <v>0.238999992609024</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1251" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="H1251" t="n">
-        <v>15000</v>
+        <v>105000</v>
       </c>
       <c r="I1251" t="s">
         <v>9</v>
@@ -36662,16 +36662,16 @@
         <v>9</v>
       </c>
       <c r="B1252" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.263999998569489</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1252" t="n">
-        <v>0.239999994635582</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="F1252" t="n">
         <v>0.243000000715256</v>
@@ -36680,7 +36680,7 @@
         <v>0.243000000715256</v>
       </c>
       <c r="H1252" t="n">
-        <v>105000</v>
+        <v>0</v>
       </c>
       <c r="I1252" t="s">
         <v>9</v>
@@ -36691,25 +36691,25 @@
         <v>9</v>
       </c>
       <c r="B1253" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46289.2916666667</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.252000004053116</v>
       </c>
       <c r="E1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="F1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.243000000715256</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="H1253" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I1253" t="s">
         <v>9</v>
@@ -36720,25 +36720,25 @@
         <v>9</v>
       </c>
       <c r="B1254" s="1" t="n">
-        <v>46289.2916666667</v>
+        <v>46290.2916666667</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.250999987125397</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.252000004053116</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="E1254" t="n">
-        <v>0.248999997973442</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1254" t="n">
-        <v>0.248999997973442</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.248999997973442</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="H1254" t="n">
-        <v>27000</v>
+        <v>9000</v>
       </c>
       <c r="I1254" t="s">
         <v>9</v>
@@ -36749,16 +36749,16 @@
         <v>9</v>
       </c>
       <c r="B1255" s="1" t="n">
-        <v>46290.2916666667</v>
+        <v>46293.2916666667</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.239999994635582</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.247999995946884</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1255" t="n">
-        <v>0.239999994635582</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1255" t="n">
         <v>0.241999998688698</v>
@@ -36767,7 +36767,7 @@
         <v>0.241999998688698</v>
       </c>
       <c r="H1255" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I1255" t="s">
         <v>9</v>
@@ -36778,7 +36778,7 @@
         <v>9</v>
       </c>
       <c r="B1256" s="1" t="n">
-        <v>46293.2916666667</v>
+        <v>46294.2916666667</v>
       </c>
       <c r="C1256" t="n">
         <v>0.241999998688698</v>
@@ -36807,7 +36807,7 @@
         <v>9</v>
       </c>
       <c r="B1257" s="1" t="n">
-        <v>46294.2916666667</v>
+        <v>46295.2916666667</v>
       </c>
       <c r="C1257" t="n">
         <v>0.241999998688698</v>
@@ -36825,7 +36825,7 @@
         <v>0.241999998688698</v>
       </c>
       <c r="H1257" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I1257" t="s">
         <v>9</v>
@@ -36836,25 +36836,25 @@
         <v>9</v>
       </c>
       <c r="B1258" s="1" t="n">
-        <v>46295.2916666667</v>
+        <v>46296.2916666667</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="E1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.241999998688698</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="H1258" t="n">
-        <v>6000</v>
+        <v>126000</v>
       </c>
       <c r="I1258" t="s">
         <v>9</v>
@@ -36865,25 +36865,25 @@
         <v>9</v>
       </c>
       <c r="B1259" s="1" t="n">
-        <v>46296.2916666667</v>
+        <v>46297.2916666667</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.24600000679493</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.261000007390976</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1259" t="n">
-        <v>0.24600000679493</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1259" t="n">
-        <v>0.254000008106232</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.254000008106232</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="H1259" t="n">
-        <v>126000</v>
+        <v>42000</v>
       </c>
       <c r="I1259" t="s">
         <v>9</v>
@@ -36894,25 +36894,25 @@
         <v>9</v>
       </c>
       <c r="B1260" s="1" t="n">
-        <v>46297.2916666667</v>
+        <v>46300.2916666667</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.250999987125397</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1260" t="n">
-        <v>0.250999987125397</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1260" t="n">
-        <v>0.257999986410141</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.257999986410141</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="H1260" t="n">
-        <v>42000</v>
+        <v>13500</v>
       </c>
       <c r="I1260" t="s">
         <v>9</v>
@@ -36923,25 +36923,25 @@
         <v>9</v>
       </c>
       <c r="B1261" s="1" t="n">
-        <v>46300.2916666667</v>
+        <v>46301.2916666667</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="F1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.256000012159348</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="H1261" t="n">
-        <v>13500</v>
+        <v>21000</v>
       </c>
       <c r="I1261" t="s">
         <v>9</v>
@@ -36952,25 +36952,25 @@
         <v>9</v>
       </c>
       <c r="B1262" s="1" t="n">
-        <v>46301.2916666667</v>
+        <v>46302.2916666667</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.261000007390976</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.263999998569489</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="E1262" t="n">
-        <v>0.261000007390976</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="F1262" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="H1262" t="n">
-        <v>21000</v>
+        <v>13500</v>
       </c>
       <c r="I1262" t="s">
         <v>9</v>
@@ -36981,25 +36981,25 @@
         <v>9</v>
       </c>
       <c r="B1263" s="1" t="n">
-        <v>46302.2916666667</v>
+        <v>46303.2916666667</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.266000002622604</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1263" t="n">
-        <v>0.266000002622604</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1263" t="n">
-        <v>0.264999985694885</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F1263" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="H1263" t="n">
-        <v>13500</v>
+        <v>10500</v>
       </c>
       <c r="I1263" t="s">
         <v>9</v>
@@ -37010,25 +37010,25 @@
         <v>9</v>
       </c>
       <c r="B1264" s="1" t="n">
-        <v>46303.2916666667</v>
+        <v>46304.2916666667</v>
       </c>
       <c r="C1264" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="D1264" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1264" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="F1264" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.263999998569489</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="H1264" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="I1264" t="s">
         <v>9</v>
@@ -37039,25 +37039,25 @@
         <v>9</v>
       </c>
       <c r="B1265" s="1" t="n">
-        <v>46304.2916666667</v>
+        <v>46307.2916666667</v>
       </c>
       <c r="C1265" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="D1265" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="E1265" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="F1265" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="H1265" t="n">
-        <v>1500</v>
+        <v>18000</v>
       </c>
       <c r="I1265" t="s">
         <v>9</v>
@@ -37068,25 +37068,25 @@
         <v>9</v>
       </c>
       <c r="B1266" s="1" t="n">
-        <v>46307.2916666667</v>
+        <v>46308.2916666667</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="D1266" t="n">
-        <v>0.261999994516373</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="E1266" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="F1266" t="n">
-        <v>0.261999994516373</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.261999994516373</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="H1266" t="n">
-        <v>18000</v>
+        <v>10500</v>
       </c>
       <c r="I1266" t="s">
         <v>9</v>
@@ -37097,25 +37097,25 @@
         <v>9</v>
       </c>
       <c r="B1267" s="1" t="n">
-        <v>46308.2916666667</v>
+        <v>46309.2916666667</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.256999999284744</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="H1267" t="n">
-        <v>10500</v>
+        <v>16500</v>
       </c>
       <c r="I1267" t="s">
         <v>9</v>
@@ -37126,13 +37126,13 @@
         <v>9</v>
       </c>
       <c r="B1268" s="1" t="n">
-        <v>46309.2916666667</v>
+        <v>46310.2916666667</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1268" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1268" t="n">
         <v>0.256000012159348</v>
@@ -37144,7 +37144,7 @@
         <v>0.256000012159348</v>
       </c>
       <c r="H1268" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="I1268" t="s">
         <v>9</v>
@@ -37155,25 +37155,25 @@
         <v>9</v>
       </c>
       <c r="B1269" s="1" t="n">
-        <v>46310.2916666667</v>
+        <v>46311.2916666667</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.256000012159348</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="D1269" t="n">
-        <v>0.256000012159348</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="E1269" t="n">
-        <v>0.256000012159348</v>
+        <v>0.24099999666214</v>
       </c>
       <c r="F1269" t="n">
-        <v>0.256000012159348</v>
+        <v>0.252999991178513</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.256000012159348</v>
+        <v>0.252999991178513</v>
       </c>
       <c r="H1269" t="n">
-        <v>0</v>
+        <v>91500</v>
       </c>
       <c r="I1269" t="s">
         <v>9</v>
@@ -37184,7 +37184,7 @@
         <v>9</v>
       </c>
       <c r="B1270" s="1" t="n">
-        <v>46311.2916666667</v>
+        <v>46314.2916666667</v>
       </c>
       <c r="C1270" t="n">
         <v>0.254000008106232</v>
@@ -37193,16 +37193,16 @@
         <v>0.254000008106232</v>
       </c>
       <c r="E1270" t="n">
-        <v>0.24099999666214</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1270" t="n">
-        <v>0.252999991178513</v>
+        <v>0.25</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.252999991178513</v>
+        <v>0.25</v>
       </c>
       <c r="H1270" t="n">
-        <v>91500</v>
+        <v>69000</v>
       </c>
       <c r="I1270" t="s">
         <v>9</v>
@@ -37213,25 +37213,25 @@
         <v>9</v>
       </c>
       <c r="B1271" s="1" t="n">
-        <v>46314.2916666667</v>
+        <v>46315.2916666667</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.254000008106232</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="D1271" t="n">
-        <v>0.254000008106232</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="E1271" t="n">
         <v>0.239999994635582</v>
       </c>
       <c r="F1271" t="n">
-        <v>0.25</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.25</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="H1271" t="n">
-        <v>69000</v>
+        <v>16500</v>
       </c>
       <c r="I1271" t="s">
         <v>9</v>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37222,7 +37222,7 @@
         <v>0.24600000679493</v>
       </c>
       <c r="E1271" t="n">
-        <v>0.239999994635582</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="F1271" t="n">
         <v>0.238999992609024</v>
@@ -37234,6 +37234,35 @@
         <v>16500</v>
       </c>
       <c r="I1271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1272" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1272" t="n">
+        <v>0.238999992609024</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I1272" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37266,6 +37266,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1273">
+      <c r="A1273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1273" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1273" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -36575,25 +36575,25 @@
         <v>9</v>
       </c>
       <c r="B1249" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="C1249" t="n">
         <v>0.237000003457069</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.244000002741814</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="E1249" t="n">
         <v>0.237000003457069</v>
       </c>
       <c r="F1249" t="n">
-        <v>0.238999992609024</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.238999992609024</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="H1249" t="n">
-        <v>25500</v>
+        <v>1500</v>
       </c>
       <c r="I1249" t="s">
         <v>9</v>
@@ -36604,25 +36604,25 @@
         <v>9</v>
       </c>
       <c r="B1250" s="1" t="n">
-        <v>46286.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.245000004768372</v>
+        <v>0.237000003457069</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.245000004768372</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="E1250" t="n">
+        <v>0.237000003457069</v>
+      </c>
+      <c r="F1250" t="n">
         <v>0.238999992609024</v>
       </c>
-      <c r="F1250" t="n">
-        <v>0.239999994635582</v>
-      </c>
       <c r="G1250" t="n">
-        <v>0.239999994635582</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="H1250" t="n">
-        <v>15000</v>
+        <v>25500</v>
       </c>
       <c r="I1250" t="s">
         <v>9</v>
@@ -36633,25 +36633,25 @@
         <v>9</v>
       </c>
       <c r="B1251" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46286.2916666667</v>
       </c>
       <c r="C1251" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>0.238999992609024</v>
+      </c>
+      <c r="F1251" t="n">
         <v>0.239999994635582</v>
       </c>
-      <c r="D1251" t="n">
-        <v>0.263999998569489</v>
-      </c>
-      <c r="E1251" t="n">
+      <c r="G1251" t="n">
         <v>0.239999994635582</v>
       </c>
-      <c r="F1251" t="n">
-        <v>0.243000000715256</v>
-      </c>
-      <c r="G1251" t="n">
-        <v>0.243000000715256</v>
-      </c>
       <c r="H1251" t="n">
-        <v>105000</v>
+        <v>15000</v>
       </c>
       <c r="I1251" t="s">
         <v>9</v>
@@ -36662,16 +36662,16 @@
         <v>9</v>
       </c>
       <c r="B1252" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1252" t="n">
-        <v>0.243000000715256</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1252" t="n">
         <v>0.243000000715256</v>
@@ -36680,7 +36680,7 @@
         <v>0.243000000715256</v>
       </c>
       <c r="H1252" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="I1252" t="s">
         <v>9</v>
@@ -36691,25 +36691,25 @@
         <v>9</v>
       </c>
       <c r="B1253" s="1" t="n">
-        <v>46289.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.250999987125397</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.252000004053116</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="E1253" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="F1253" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.248999997973442</v>
+        <v>0.243000000715256</v>
       </c>
       <c r="H1253" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I1253" t="s">
         <v>9</v>
@@ -36720,25 +36720,25 @@
         <v>9</v>
       </c>
       <c r="B1254" s="1" t="n">
-        <v>46290.2916666667</v>
+        <v>46289.2916666667</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.239999994635582</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.247999995946884</v>
+        <v>0.252000004053116</v>
       </c>
       <c r="E1254" t="n">
-        <v>0.239999994635582</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="F1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.241999998688698</v>
+        <v>0.248999997973442</v>
       </c>
       <c r="H1254" t="n">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="I1254" t="s">
         <v>9</v>
@@ -36749,16 +36749,16 @@
         <v>9</v>
       </c>
       <c r="B1255" s="1" t="n">
-        <v>46293.2916666667</v>
+        <v>46290.2916666667</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.247999995946884</v>
       </c>
       <c r="E1255" t="n">
-        <v>0.241999998688698</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F1255" t="n">
         <v>0.241999998688698</v>
@@ -36767,7 +36767,7 @@
         <v>0.241999998688698</v>
       </c>
       <c r="H1255" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I1255" t="s">
         <v>9</v>
@@ -36778,7 +36778,7 @@
         <v>9</v>
       </c>
       <c r="B1256" s="1" t="n">
-        <v>46294.2916666667</v>
+        <v>46293.2916666667</v>
       </c>
       <c r="C1256" t="n">
         <v>0.241999998688698</v>
@@ -36807,7 +36807,7 @@
         <v>9</v>
       </c>
       <c r="B1257" s="1" t="n">
-        <v>46295.2916666667</v>
+        <v>46294.2916666667</v>
       </c>
       <c r="C1257" t="n">
         <v>0.241999998688698</v>
@@ -36825,7 +36825,7 @@
         <v>0.241999998688698</v>
       </c>
       <c r="H1257" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="I1257" t="s">
         <v>9</v>
@@ -36836,25 +36836,25 @@
         <v>9</v>
       </c>
       <c r="B1258" s="1" t="n">
-        <v>46296.2916666667</v>
+        <v>46295.2916666667</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.261000007390976</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1258" t="n">
-        <v>0.24600000679493</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1258" t="n">
-        <v>0.254000008106232</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.254000008106232</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="H1258" t="n">
-        <v>126000</v>
+        <v>6000</v>
       </c>
       <c r="I1258" t="s">
         <v>9</v>
@@ -36865,25 +36865,25 @@
         <v>9</v>
       </c>
       <c r="B1259" s="1" t="n">
-        <v>46297.2916666667</v>
+        <v>46296.2916666667</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.250999987125397</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.259999990463257</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="E1259" t="n">
-        <v>0.250999987125397</v>
+        <v>0.24600000679493</v>
       </c>
       <c r="F1259" t="n">
-        <v>0.257999986410141</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.257999986410141</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="H1259" t="n">
-        <v>42000</v>
+        <v>126000</v>
       </c>
       <c r="I1259" t="s">
         <v>9</v>
@@ -36894,25 +36894,25 @@
         <v>9</v>
       </c>
       <c r="B1260" s="1" t="n">
-        <v>46300.2916666667</v>
+        <v>46297.2916666667</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.250999987125397</v>
       </c>
       <c r="F1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.256000012159348</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="H1260" t="n">
-        <v>13500</v>
+        <v>42000</v>
       </c>
       <c r="I1260" t="s">
         <v>9</v>
@@ -36923,25 +36923,25 @@
         <v>9</v>
       </c>
       <c r="B1261" s="1" t="n">
-        <v>46301.2916666667</v>
+        <v>46300.2916666667</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.261000007390976</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.263999998569489</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1261" t="n">
-        <v>0.261000007390976</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1261" t="n">
-        <v>0.263999998569489</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.263999998569489</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="H1261" t="n">
-        <v>21000</v>
+        <v>13500</v>
       </c>
       <c r="I1261" t="s">
         <v>9</v>
@@ -36952,25 +36952,25 @@
         <v>9</v>
       </c>
       <c r="B1262" s="1" t="n">
-        <v>46302.2916666667</v>
+        <v>46301.2916666667</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.266000002622604</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.266000002622604</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1262" t="n">
-        <v>0.264999985694885</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="F1262" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.264999985694885</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="H1262" t="n">
-        <v>13500</v>
+        <v>21000</v>
       </c>
       <c r="I1262" t="s">
         <v>9</v>
@@ -36981,25 +36981,25 @@
         <v>9</v>
       </c>
       <c r="B1263" s="1" t="n">
-        <v>46303.2916666667</v>
+        <v>46302.2916666667</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.259999990463257</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="D1263" t="n">
-        <v>0.263999998569489</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="E1263" t="n">
-        <v>0.259999990463257</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="F1263" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.263999998569489</v>
+        <v>0.264999985694885</v>
       </c>
       <c r="H1263" t="n">
-        <v>10500</v>
+        <v>13500</v>
       </c>
       <c r="I1263" t="s">
         <v>9</v>
@@ -37010,25 +37010,25 @@
         <v>9</v>
       </c>
       <c r="B1264" s="1" t="n">
-        <v>46304.2916666667</v>
+        <v>46303.2916666667</v>
       </c>
       <c r="C1264" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="D1264" t="n">
-        <v>0.259999990463257</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="E1264" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="F1264" t="n">
-        <v>0.259999990463257</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.259999990463257</v>
+        <v>0.263999998569489</v>
       </c>
       <c r="H1264" t="n">
-        <v>1500</v>
+        <v>10500</v>
       </c>
       <c r="I1264" t="s">
         <v>9</v>
@@ -37039,25 +37039,25 @@
         <v>9</v>
       </c>
       <c r="B1265" s="1" t="n">
-        <v>46307.2916666667</v>
+        <v>46304.2916666667</v>
       </c>
       <c r="C1265" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="D1265" t="n">
-        <v>0.261999994516373</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1265" t="n">
         <v>0.259999990463257</v>
       </c>
       <c r="F1265" t="n">
-        <v>0.261999994516373</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.261999994516373</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="H1265" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="I1265" t="s">
         <v>9</v>
@@ -37068,25 +37068,25 @@
         <v>9</v>
       </c>
       <c r="B1266" s="1" t="n">
-        <v>46308.2916666667</v>
+        <v>46307.2916666667</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="E1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.256999999284744</v>
+        <v>0.261999994516373</v>
       </c>
       <c r="H1266" t="n">
-        <v>10500</v>
+        <v>18000</v>
       </c>
       <c r="I1266" t="s">
         <v>9</v>
@@ -37097,25 +37097,25 @@
         <v>9</v>
       </c>
       <c r="B1267" s="1" t="n">
-        <v>46309.2916666667</v>
+        <v>46308.2916666667</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="D1267" t="n">
-        <v>0.259999990463257</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="E1267" t="n">
-        <v>0.256000012159348</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="F1267" t="n">
-        <v>0.256000012159348</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.256000012159348</v>
+        <v>0.256999999284744</v>
       </c>
       <c r="H1267" t="n">
-        <v>16500</v>
+        <v>10500</v>
       </c>
       <c r="I1267" t="s">
         <v>9</v>
@@ -37126,13 +37126,13 @@
         <v>9</v>
       </c>
       <c r="B1268" s="1" t="n">
-        <v>46310.2916666667</v>
+        <v>46309.2916666667</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.256000012159348</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D1268" t="n">
-        <v>0.256000012159348</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E1268" t="n">
         <v>0.256000012159348</v>
@@ -37144,7 +37144,7 @@
         <v>0.256000012159348</v>
       </c>
       <c r="H1268" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="I1268" t="s">
         <v>9</v>
@@ -37155,25 +37155,25 @@
         <v>9</v>
       </c>
       <c r="B1269" s="1" t="n">
-        <v>46311.2916666667</v>
+        <v>46310.2916666667</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.254000008106232</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="D1269" t="n">
-        <v>0.254000008106232</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="E1269" t="n">
-        <v>0.24099999666214</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="F1269" t="n">
-        <v>0.252999991178513</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.252999991178513</v>
+        <v>0.256000012159348</v>
       </c>
       <c r="H1269" t="n">
-        <v>91500</v>
+        <v>0</v>
       </c>
       <c r="I1269" t="s">
         <v>9</v>
@@ -37184,7 +37184,7 @@
         <v>9</v>
       </c>
       <c r="B1270" s="1" t="n">
-        <v>46314.2916666667</v>
+        <v>46311.2916666667</v>
       </c>
       <c r="C1270" t="n">
         <v>0.254000008106232</v>
@@ -37193,16 +37193,16 @@
         <v>0.254000008106232</v>
       </c>
       <c r="E1270" t="n">
-        <v>0.239999994635582</v>
+        <v>0.24099999666214</v>
       </c>
       <c r="F1270" t="n">
-        <v>0.25</v>
+        <v>0.252999991178513</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.25</v>
+        <v>0.252999991178513</v>
       </c>
       <c r="H1270" t="n">
-        <v>69000</v>
+        <v>91500</v>
       </c>
       <c r="I1270" t="s">
         <v>9</v>
@@ -37213,25 +37213,25 @@
         <v>9</v>
       </c>
       <c r="B1271" s="1" t="n">
-        <v>46315.2916666667</v>
+        <v>46314.2916666667</v>
       </c>
       <c r="C1271" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="E1271" t="n">
         <v>0.239999994635582</v>
       </c>
-      <c r="D1271" t="n">
-        <v>0.24600000679493</v>
-      </c>
-      <c r="E1271" t="n">
-        <v>0.238999992609024</v>
-      </c>
       <c r="F1271" t="n">
-        <v>0.238999992609024</v>
+        <v>0.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.238999992609024</v>
+        <v>0.25</v>
       </c>
       <c r="H1271" t="n">
-        <v>16500</v>
+        <v>69000</v>
       </c>
       <c r="I1271" t="s">
         <v>9</v>
@@ -37242,25 +37242,25 @@
         <v>9</v>
       </c>
       <c r="B1272" s="1" t="n">
-        <v>46316.2916666667</v>
+        <v>46315.2916666667</v>
       </c>
       <c r="C1272" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="E1272" t="n">
         <v>0.238999992609024</v>
       </c>
-      <c r="D1272" t="n">
-        <v>0.239999994635582</v>
-      </c>
-      <c r="E1272" t="n">
-        <v>0.234999999403954</v>
-      </c>
       <c r="F1272" t="n">
-        <v>0.239999994635582</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.239999994635582</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="H1272" t="n">
-        <v>33000</v>
+        <v>16500</v>
       </c>
       <c r="I1272" t="s">
         <v>9</v>
@@ -37271,27 +37271,85 @@
         <v>9</v>
       </c>
       <c r="B1273" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1273" t="n">
+        <v>0.238999992609024</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1274" s="1" t="n">
         <v>46317.2916666667</v>
       </c>
-      <c r="C1273" t="n">
+      <c r="C1274" t="n">
         <v>0.234999999403954</v>
       </c>
-      <c r="D1273" t="n">
+      <c r="D1274" t="n">
         <v>0.234999999403954</v>
       </c>
-      <c r="E1273" t="n">
+      <c r="E1274" t="n">
         <v>0.232999995350838</v>
       </c>
-      <c r="F1273" t="n">
+      <c r="F1274" t="n">
         <v>0.232999995350838</v>
       </c>
-      <c r="G1273" t="n">
+      <c r="G1274" t="n">
         <v>0.232999995350838</v>
       </c>
-      <c r="H1273" t="n">
+      <c r="H1274" t="n">
         <v>12000</v>
       </c>
-      <c r="I1273" t="s">
+      <c r="I1274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1275" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1275" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>144000</v>
+      </c>
+      <c r="I1275" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37353,6 +37353,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1276">
+      <c r="A1276" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1276" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1276" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>0.229000002145767</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37382,6 +37382,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1277">
+      <c r="A1277" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1277" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1277" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1278" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1278" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37440,6 +37440,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1279">
+      <c r="A1279" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1279" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1279" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I1279" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIT.MI.xlsx
+++ b/data/DIT.MI.xlsx
@@ -37469,6 +37469,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1280">
+      <c r="A1280" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1280" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1280" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1280" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
